--- a/reports/firm_B_report.xlsx
+++ b/reports/firm_B_report.xlsx
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(AssetClass:High Yield Bonds)&lt;-[:BELONGS_TO]-(Position:HY-01) | (AssetClass:High Yield Bonds)&lt;-[:BELONGS_TO]-(Position:HY-02) | (AssetClass:Structured Credit)&lt;-[:BELONGS_TO]-(Position:SC-01) | (Position:COR-05)-[:FALLEN_ANGEL]-&gt;(Aggregate:non_ig)-[:CONTRIBUTES_TO]-&gt;(Aggregate:non_ig) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(Position:SC-01)-&gt;(AssetClass:Structured Credit) | (Position:HY-01)-&gt;(AssetClass:High Yield Bonds) | (Position:HY-02)-&gt;(AssetClass:High Yield Bonds) | (Position:COR-05)-[:FALLEN_ANGEL]-&gt;(Aggregate:non_ig)-[:CONTRIBUTES_TO]-&gt;(Aggregate:non_ig) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>(Position:COR-03 | Position:COR-04)-[:ISSUED_BY]-&gt;(Issuer)-[:GROUPED_UNDER]-&gt;(ParentIssuer:Redhill Holdings)&lt;-[:GOVERNS]-(RiskMetric:gre_concentration) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(Position:COR-03 | Position:COR-04)-[:ISSUED_BY]-&gt;(Issuer)-[:GROUPED_UNDER]-&gt;(ParentIssuer:Redhill Holdings) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities) | (AssetClass:Cash &amp; Cash Equivalents) | (AssetClass:MAS Bills)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(AssetClass:Cash &amp; Cash Equivalents) | (AssetClass:MAS Bills) | (AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>(Position:*)-[:BELONGS_TO]-&gt;(AssetClass:*) | weighted_avg(modified_duration)-&gt;(RiskMetric:modified_duration) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(Position:*)-weighted_avg(modified_duration)-&gt;(RiskMetric:modified_duration) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>(Position:*) -&gt; sum(MV * duration / 10000) -&gt; (RiskMetric:dv01) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(Position:*)-&gt;sum(MV*duration/10000)-&gt;(RiskMetric:dv01) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>

--- a/reports/firm_B_report.xlsx
+++ b/reports/firm_B_report.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Narrative" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,8 +50,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -856,7 +861,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(AssetClass:Cash &amp; Cash Equivalents) | (AssetClass:MAS Bills) | (AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities) | (AssetClass:Cash &amp; Cash Equivalents) | (AssetClass:MAS Bills)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -931,6 +936,37 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>(Position:*)-&gt;sum(MV*duration/10000)-&gt;(RiskMetric:dv01) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Compliance Commentary — firm_B (LLM-generated, Gemini)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>The Meridian Fixed Income Fund maintains compliance with its duration and liquidity mandates, with a portfolio modified duration of 3.88 yrs and a liquid assets ratio of 47.0%. However, the fund is currently in breach of its cash requirements, holding 4.0% in Cash &amp; Cash Equivalents against a 5.0% minimum, and exceeds the aggregate non-ig-exposure limit of 20.0% with a current value of 21.0%. Furthermore, the largest_gre_issuer is at 13.0%, exceeding the 12.0% limit, while the largest_single_corporate_issuer remains at the 8.0% limit. All other asset allocations, including Singapore Government Securities at 35.0%, MAS Bills at 8.0%, Investment Grade Corporate Bonds at 33.0%, High Yield Bonds at 9.0%, Foreign Currency Bonds at 5.0%, and Structured Credit at 6.0%, remain within their respective prescribed ranges.</t>
         </is>
       </c>
     </row>

--- a/reports/firm_B_report.xlsx
+++ b/reports/firm_B_report.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>(Position:SC-01)-&gt;(AssetClass:Structured Credit) | (Position:HY-01)-&gt;(AssetClass:High Yield Bonds) | (Position:HY-02)-&gt;(AssetClass:High Yield Bonds) | (Position:COR-05)-[:FALLEN_ANGEL]-&gt;(Aggregate:non_ig)-[:CONTRIBUTES_TO]-&gt;(Aggregate:non_ig) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(Position:HY-01)-&gt;(AssetClass:High Yield Bonds) | (Position:HY-02)-&gt;(AssetClass:High Yield Bonds) | (Position:SC-01)-&gt;(AssetClass:Structured Credit) | (Position:COR-05)-[:FALLEN_ANGEL]-&gt;(Aggregate:non_ig)-[:CONTRIBUTES_TO]-&gt;(Aggregate:non_ig) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>(AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities) | (AssetClass:Cash &amp; Cash Equivalents) | (AssetClass:MAS Bills)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
+          <t>(AssetClass:MAS Bills) | (AssetClass:Singapore Government Securities) | (AssetClass:Singapore Government Securities) | (AssetClass:Cash &amp; Cash Equivalents)-[:CONTRIBUTES_TO]-&gt;(Aggregate:liquidity) | sample_fund_guidelines.pdf p2 [p2_7f6467ea]</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>The Meridian Fixed Income Fund maintains compliance with its duration and liquidity mandates, with a portfolio modified duration of 3.88 yrs and a liquid assets ratio of 47.0%. However, the fund is currently in breach of its cash requirements, holding 4.0% in Cash &amp; Cash Equivalents against a 5.0% minimum, and exceeds the aggregate non-ig-exposure limit of 20.0% with a current value of 21.0%. Furthermore, the largest_gre_issuer is at 13.0%, exceeding the 12.0% limit, while the largest_single_corporate_issuer remains at the 8.0% limit. All other asset allocations, including Singapore Government Securities at 35.0%, MAS Bills at 8.0%, Investment Grade Corporate Bonds at 33.0%, High Yield Bonds at 9.0%, Foreign Currency Bonds at 5.0%, and Structured Credit at 6.0%, remain within their respective prescribed ranges.</t>
+          <t>The Meridian Fixed Income Fund maintains compliance with its duration and liquidity mandates, with a portfolio modified duration of 3.88 yrs and a liquid assets ratio of 47.0%. However, the fund is currently in breach of its cash requirements with an allocation of 4.0%, and its aggregate non-ig exposure of 21.0% exceeds the maximum limit of 20.0%. Furthermore, the largest gre issuer exposure of 13.0% is in breach of the 12.0% limit, while the largest single corporate issuer is currently at the limit of 8.0%. All other asset allocations, including Singapore Government Securities at 35.0%, MAS Bills at 8.0%, Investment Grade Corporate Bonds at 33.0%, High Yield Bonds at 9.0%, Foreign Currency Bonds at 5.0%, and Structured Credit at 6.0%, remain within their respective thresholds.</t>
         </is>
       </c>
     </row>
